--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-01-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-01-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-08-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2015-03-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1245,7 +1245,7 @@
           <t>- | 2363呎 (4+房)
 $8364万
 $35,396/呎
-(已售)</t>
+(16年-01月)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
           <t>- | 2406呎 (4+房)
 $8439万
 $35,075/呎
-(已售)</t>
+(16年-01月)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
           <t>- | 2406呎 (4+房)
 $9638万
 $40,058/呎
-(已售)</t>
+(14年-08月)</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
           <t>- | 2433呎 (4+房)
 $8924万
 $36,681/呎
-(已售)</t>
+(17年-06月)</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
           <t>- | 1506呎 (3房)
 $5065万
 $33,634/呎
-(已售)</t>
+(15年-03月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -199,61 +199,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -199,61 +199,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
